--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00900-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00900-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D746FBA0-D928-4DDD-B334-2475C9A3ED50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{647A232A-BC50-4055-8B5E-C2C8E1F800B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{87A25A3E-2F4F-4943-9E01-86DE894C3117}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{471DEF64-2941-4F6D-B7CA-CC74D06415FB}"/>
   </bookViews>
   <sheets>
     <sheet name="00900-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1606,24 +1606,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1859457A-F8D6-43A6-BA25-06ED6F750F87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28CA146D-5B00-45C7-B39D-0AB025FA6C82}">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1651,7 +1652,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1681,7 +1682,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1727,7 +1728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1777,7 +1778,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1831,7 +1832,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1857,7 +1858,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1913,7 +1914,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1969,7 +1970,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2023,7 +2024,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2135,7 +2136,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2191,7 +2192,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2247,7 +2248,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2303,7 +2304,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2359,7 +2360,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2415,7 +2416,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2471,7 +2472,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2527,7 +2528,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2583,7 +2584,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2639,7 +2640,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2749,7 +2750,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2805,7 +2806,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2917,7 +2918,7 @@
         <v>5.0199999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2973,7 +2974,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3029,7 +3030,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2023</v>
       </c>
@@ -3083,7 +3084,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>26</v>
       </c>
@@ -3139,7 +3140,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>26</v>
       </c>
@@ -3195,7 +3196,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>26</v>
       </c>
@@ -3251,7 +3252,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>26</v>
       </c>
@@ -3307,7 +3308,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2022</v>
       </c>
@@ -3361,7 +3362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>26</v>
       </c>
@@ -3417,7 +3418,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>26</v>
       </c>
@@ -3473,7 +3474,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="49" t="s">
         <v>73</v>
       </c>
